--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/5314-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/5314-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{94C09FB2-2E49-4689-A287-E5482768E5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B614C20-E145-4456-A4DF-09CE99D38AD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{1F1888E3-D872-4926-B6EC-0823425D9732}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{2F272D90-389D-42B0-9A29-0780C58FCE10}"/>
   </bookViews>
   <sheets>
     <sheet name="5314-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1448,30 +1448,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5DDCED8-B95F-4092-88A0-B2A1CEBF9852}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D212782-542C-4423-87B4-732BDC39E13D}">
   <dimension ref="A1:X40"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1505,7 +1505,7 @@
       <c r="W1" s="27"/>
       <c r="X1" s="19"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1541,7 +1541,7 @@
       <c r="W2" s="29"/>
       <c r="X2" s="30"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="X3" s="33"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1661,7 +1661,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="34">
         <v>2024</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>0.61</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="36">
         <v>2023</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>30</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>2.58</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="15" t="s">
         <v>30</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="34">
         <v>2022</v>
       </c>
@@ -2025,7 +2025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2021</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="34">
         <v>2020</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2019</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="34">
         <v>2018</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2017</v>
       </c>
@@ -2385,7 +2385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="34">
         <v>2016</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2015</v>
       </c>
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="34">
         <v>2014</v>
       </c>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2013</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="34">
         <v>2012</v>
       </c>
@@ -2745,7 +2745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2011</v>
       </c>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="34">
         <v>2010</v>
       </c>
@@ -2889,7 +2889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2009</v>
       </c>
@@ -2961,7 +2961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="34">
         <v>2008</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="36">
         <v>2007</v>
       </c>
@@ -3105,7 +3105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="34">
         <v>2006</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2005</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>1.82</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="34">
         <v>2004</v>
       </c>
@@ -3321,7 +3321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2003</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="34">
         <v>2002</v>
       </c>
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2001</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="34">
         <v>2000</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>1999</v>
       </c>
@@ -3681,7 +3681,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="34">
         <v>1998</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>1997</v>
       </c>
@@ -3825,7 +3825,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="34">
         <v>1996</v>
       </c>
@@ -3897,7 +3897,7 @@
         <v>3.16</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>1995</v>
       </c>
@@ -3969,7 +3969,7 @@
         <v>5.61</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="34">
         <v>1994</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>1993</v>
       </c>
@@ -4113,7 +4113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="34">
         <v>1992</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36" t="s">
         <v>38</v>
       </c>
